--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/141.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/141.xlsx
@@ -426,13 +426,13 @@
         <v>-10.48124939585953</v>
       </c>
       <c r="E2">
-        <v>-5.783239247845285</v>
+        <v>-8.749249340175131</v>
       </c>
       <c r="F2">
-        <v>-4.741498122703417</v>
+        <v>-6.516163867785682</v>
       </c>
       <c r="G2">
-        <v>-10.64243430451761</v>
+        <v>-12.26652413368816</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-11.01827154158138</v>
       </c>
       <c r="E3">
-        <v>-6.155470754327773</v>
+        <v>-9.196599173496855</v>
       </c>
       <c r="F3">
-        <v>-4.852471190186856</v>
+        <v>-6.175891662084417</v>
       </c>
       <c r="G3">
-        <v>-11.91648998016972</v>
+        <v>-14.09236643288429</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-11.68616390480029</v>
       </c>
       <c r="E4">
-        <v>-6.926497795821743</v>
+        <v>-9.282454512208277</v>
       </c>
       <c r="F4">
-        <v>-4.681158184348696</v>
+        <v>-6.131781926252746</v>
       </c>
       <c r="G4">
-        <v>-12.07792936211596</v>
+        <v>-14.48816214288153</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-12.34613145314832</v>
       </c>
       <c r="E5">
-        <v>-7.674565474096825</v>
+        <v>-11.7417238346058</v>
       </c>
       <c r="F5">
-        <v>-4.484153363512709</v>
+        <v>-5.769125990776733</v>
       </c>
       <c r="G5">
-        <v>-12.36030800830021</v>
+        <v>-14.15352019969844</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-12.95104173533149</v>
       </c>
       <c r="E6">
-        <v>-8.449518702555446</v>
+        <v>-11.78424167706382</v>
       </c>
       <c r="F6">
-        <v>-4.256008555270683</v>
+        <v>-6.127780083329821</v>
       </c>
       <c r="G6">
-        <v>-12.23056522661821</v>
+        <v>-14.46762661775175</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-13.43419025458165</v>
       </c>
       <c r="E7">
-        <v>-9.059553964602728</v>
+        <v>-11.48948783237856</v>
       </c>
       <c r="F7">
-        <v>-4.176216893563423</v>
+        <v>-6.008464527732788</v>
       </c>
       <c r="G7">
-        <v>-12.5267348470168</v>
+        <v>-14.54989504530092</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-13.74567396384652</v>
       </c>
       <c r="E8">
-        <v>-9.837255976784004</v>
+        <v>-12.03958421246032</v>
       </c>
       <c r="F8">
-        <v>-3.948293259417945</v>
+        <v>-5.531769737015576</v>
       </c>
       <c r="G8">
-        <v>-12.17941754494958</v>
+        <v>-14.33883046848964</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-13.85754926622083</v>
       </c>
       <c r="E9">
-        <v>-10.96006393614182</v>
+        <v>-13.10796444271995</v>
       </c>
       <c r="F9">
-        <v>-3.738114911775238</v>
+        <v>-5.435995554638703</v>
       </c>
       <c r="G9">
-        <v>-12.6322950258057</v>
+        <v>-14.82738959319394</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-13.75245305484519</v>
       </c>
       <c r="E10">
-        <v>-10.95686683349241</v>
+        <v>-14.3000444689731</v>
       </c>
       <c r="F10">
-        <v>-3.770948910520002</v>
+        <v>-5.428607345773135</v>
       </c>
       <c r="G10">
-        <v>-12.33203044090091</v>
+        <v>-14.50791837789095</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-13.43654973240809</v>
       </c>
       <c r="E11">
-        <v>-12.94505259029401</v>
+        <v>-14.3297376730414</v>
       </c>
       <c r="F11">
-        <v>-3.842475950649531</v>
+        <v>-5.296159681739522</v>
       </c>
       <c r="G11">
-        <v>-11.87283004609974</v>
+        <v>-14.75296164456106</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-12.94121437875272</v>
       </c>
       <c r="E12">
-        <v>-12.18216321659182</v>
+        <v>-15.41884925730814</v>
       </c>
       <c r="F12">
-        <v>-3.602140059340505</v>
+        <v>-5.753166664394398</v>
       </c>
       <c r="G12">
-        <v>-11.99286041196579</v>
+        <v>-13.73190783847149</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-12.30525417623888</v>
       </c>
       <c r="E13">
-        <v>-13.07846596303399</v>
+        <v>-16.84764620536425</v>
       </c>
       <c r="F13">
-        <v>-3.582317227391512</v>
+        <v>-4.812772510775092</v>
       </c>
       <c r="G13">
-        <v>-11.95876851996316</v>
+        <v>-13.23437293219133</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-11.60186990251882</v>
       </c>
       <c r="E14">
-        <v>-14.05215127331922</v>
+        <v>-16.89412193410497</v>
       </c>
       <c r="F14">
-        <v>-3.603591359030209</v>
+        <v>-4.744288892483449</v>
       </c>
       <c r="G14">
-        <v>-10.94604901663459</v>
+        <v>-13.22193054003792</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-10.89542706642003</v>
       </c>
       <c r="E15">
-        <v>-15.06218211599002</v>
+        <v>-18.00313616163542</v>
       </c>
       <c r="F15">
-        <v>-3.171539772752071</v>
+        <v>-5.025385430214627</v>
       </c>
       <c r="G15">
-        <v>-9.448233717957702</v>
+        <v>-11.85879626149</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-10.25384390240703</v>
       </c>
       <c r="E16">
-        <v>-14.96407725508785</v>
+        <v>-17.94398070567323</v>
       </c>
       <c r="F16">
-        <v>-3.45352680544126</v>
+        <v>-4.536686767463448</v>
       </c>
       <c r="G16">
-        <v>-10.09008331086536</v>
+        <v>-12.37424991870629</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-9.725817383081115</v>
       </c>
       <c r="E17">
-        <v>-16.41216550241663</v>
+        <v>-19.51795600194123</v>
       </c>
       <c r="F17">
-        <v>-3.121883288791255</v>
+        <v>-4.497216717454857</v>
       </c>
       <c r="G17">
-        <v>-8.898602856978236</v>
+        <v>-10.8110136245772</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.324743536905672</v>
       </c>
       <c r="E18">
-        <v>-16.9840574278973</v>
+        <v>-21.51401677504217</v>
       </c>
       <c r="F18">
-        <v>-2.992044153709058</v>
+        <v>-4.35318930549751</v>
       </c>
       <c r="G18">
-        <v>-8.242821197329175</v>
+        <v>-11.50593697620888</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-9.058105442455973</v>
       </c>
       <c r="E19">
-        <v>-17.54659805455213</v>
+        <v>-21.40689572239073</v>
       </c>
       <c r="F19">
-        <v>-2.706258228110631</v>
+        <v>-4.46793227303109</v>
       </c>
       <c r="G19">
-        <v>-7.717025129757516</v>
+        <v>-11.11572754591659</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-8.895604274797879</v>
       </c>
       <c r="E20">
-        <v>-18.4052963528346</v>
+        <v>-21.718187554152</v>
       </c>
       <c r="F20">
-        <v>-2.531203486714026</v>
+        <v>-3.725171671106496</v>
       </c>
       <c r="G20">
-        <v>-6.785971949821959</v>
+        <v>-11.23718196193944</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-8.806000910754328</v>
       </c>
       <c r="E21">
-        <v>-19.77434914330751</v>
+        <v>-22.77212648080117</v>
       </c>
       <c r="F21">
-        <v>-2.057200061688509</v>
+        <v>-3.755506485397014</v>
       </c>
       <c r="G21">
-        <v>-6.261508058203435</v>
+        <v>-10.95657517539728</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-8.750877260888993</v>
       </c>
       <c r="E22">
-        <v>-18.90307527270575</v>
+        <v>-22.32369434219161</v>
       </c>
       <c r="F22">
-        <v>-2.087445412299525</v>
+        <v>-2.993389422371204</v>
       </c>
       <c r="G22">
-        <v>-6.659703981771408</v>
+        <v>-10.52701733616414</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-8.687240039816155</v>
       </c>
       <c r="E23">
-        <v>-20.47800607698937</v>
+        <v>-23.43264969955997</v>
       </c>
       <c r="F23">
-        <v>-1.782256637025325</v>
+        <v>-3.251371196094665</v>
       </c>
       <c r="G23">
-        <v>-6.337963801760056</v>
+        <v>-9.422627064907795</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-8.595759575875547</v>
       </c>
       <c r="E24">
-        <v>-20.65232515544064</v>
+        <v>-23.32152547588574</v>
       </c>
       <c r="F24">
-        <v>-2.001543712629216</v>
+        <v>-3.180881271953441</v>
       </c>
       <c r="G24">
-        <v>-6.605193048004352</v>
+        <v>-10.31646134869457</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-8.452137734247238</v>
       </c>
       <c r="E25">
-        <v>-20.70622758155394</v>
+        <v>-24.60693282296297</v>
       </c>
       <c r="F25">
-        <v>-1.682600724998934</v>
+        <v>-2.964515019811822</v>
       </c>
       <c r="G25">
-        <v>-6.438779334173995</v>
+        <v>-10.58382840624436</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-8.26008527936931</v>
       </c>
       <c r="E26">
-        <v>-21.63519421101342</v>
+        <v>-24.19936110532463</v>
       </c>
       <c r="F26">
-        <v>-1.886895178979556</v>
+        <v>-3.111345627060242</v>
       </c>
       <c r="G26">
-        <v>-6.575852364819798</v>
+        <v>-10.37405991194906</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-8.029131491591494</v>
       </c>
       <c r="E27">
-        <v>-21.70049933467804</v>
+        <v>-25.66924942652633</v>
       </c>
       <c r="F27">
-        <v>-1.933700422339937</v>
+        <v>-3.193619077506289</v>
       </c>
       <c r="G27">
-        <v>-6.823932402043175</v>
+        <v>-9.216179166830653</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-7.775347814436649</v>
       </c>
       <c r="E28">
-        <v>-20.69409579968739</v>
+        <v>-26.50307281708467</v>
       </c>
       <c r="F28">
-        <v>-2.019442247101505</v>
+        <v>-3.117826773619746</v>
       </c>
       <c r="G28">
-        <v>-6.392651921491321</v>
+        <v>-10.54449968463286</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-7.52907892372798</v>
       </c>
       <c r="E29">
-        <v>-20.55840460452155</v>
+        <v>-24.18058152361482</v>
       </c>
       <c r="F29">
-        <v>-2.134004630541274</v>
+        <v>-2.989390064550488</v>
       </c>
       <c r="G29">
-        <v>-7.321824961473316</v>
+        <v>-10.48186772750618</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.30766511474315</v>
       </c>
       <c r="E30">
-        <v>-20.61019676174728</v>
+        <v>-24.3660089488069</v>
       </c>
       <c r="F30">
-        <v>-2.277279056529476</v>
+        <v>-3.130393935487617</v>
       </c>
       <c r="G30">
-        <v>-6.908062922827337</v>
+        <v>-10.79513251222948</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.140510879527317</v>
       </c>
       <c r="E31">
-        <v>-19.93998260861207</v>
+        <v>-23.30747814951395</v>
       </c>
       <c r="F31">
-        <v>-2.230191339884741</v>
+        <v>-3.483885642386459</v>
       </c>
       <c r="G31">
-        <v>-7.532029858236023</v>
+        <v>-9.2693152687643</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-7.041430770191862</v>
       </c>
       <c r="E32">
-        <v>-20.28566820046159</v>
+        <v>-23.01335829118977</v>
       </c>
       <c r="F32">
-        <v>-2.222847862858924</v>
+        <v>-3.176606067787593</v>
       </c>
       <c r="G32">
-        <v>-7.187399876625985</v>
+        <v>-9.911502827492583</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-7.01829925172833</v>
       </c>
       <c r="E33">
-        <v>-20.36128918791568</v>
+        <v>-24.07882671266247</v>
       </c>
       <c r="F33">
-        <v>-2.32522744690572</v>
+        <v>-3.167384681859629</v>
       </c>
       <c r="G33">
-        <v>-7.508332876133713</v>
+        <v>-10.2414985609475</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-7.076640954456871</v>
       </c>
       <c r="E34">
-        <v>-20.73193120002147</v>
+        <v>-23.96695981925098</v>
       </c>
       <c r="F34">
-        <v>-2.20530883983945</v>
+        <v>-3.036428079151055</v>
       </c>
       <c r="G34">
-        <v>-7.16787004590417</v>
+        <v>-9.654704584585762</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-7.201209192456305</v>
       </c>
       <c r="E35">
-        <v>-20.48975746703928</v>
+        <v>-23.71848245045011</v>
       </c>
       <c r="F35">
-        <v>-1.866795672318029</v>
+        <v>-3.650998825492425</v>
       </c>
       <c r="G35">
-        <v>-6.936780173915598</v>
+        <v>-10.7067724968552</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-7.384619538683189</v>
       </c>
       <c r="E36">
-        <v>-19.45567589891374</v>
+        <v>-21.97727966602685</v>
       </c>
       <c r="F36">
-        <v>-1.920791144734709</v>
+        <v>-3.025065363486855</v>
       </c>
       <c r="G36">
-        <v>-7.680810287405925</v>
+        <v>-10.50050178474227</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-7.603243215762225</v>
       </c>
       <c r="E37">
-        <v>-18.96608898852248</v>
+        <v>-23.03130916215617</v>
       </c>
       <c r="F37">
-        <v>-2.012761463997927</v>
+        <v>-2.879676943886707</v>
       </c>
       <c r="G37">
-        <v>-6.624739284833965</v>
+        <v>-10.15939255386551</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-7.83691798139536</v>
       </c>
       <c r="E38">
-        <v>-19.19191493033698</v>
+        <v>-22.23432037917623</v>
       </c>
       <c r="F38">
-        <v>-1.954850298868213</v>
+        <v>-3.048117171571959</v>
       </c>
       <c r="G38">
-        <v>-7.318973579938159</v>
+        <v>-10.34604484227452</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-8.070443657494906</v>
       </c>
       <c r="E39">
-        <v>-17.87898351824113</v>
+        <v>-23.25291003772152</v>
       </c>
       <c r="F39">
-        <v>-2.030623550304492</v>
+        <v>-3.055305743893453</v>
       </c>
       <c r="G39">
-        <v>-6.970543943762284</v>
+        <v>-8.080256356388047</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-8.282673854217162</v>
       </c>
       <c r="E40">
-        <v>-19.36419619548479</v>
+        <v>-21.60348130753771</v>
       </c>
       <c r="F40">
-        <v>-1.840982087311991</v>
+        <v>-2.787651124007502</v>
       </c>
       <c r="G40">
-        <v>-7.376929796342631</v>
+        <v>-9.495414402760957</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-8.470478455882425</v>
       </c>
       <c r="E41">
-        <v>-16.74132216413815</v>
+        <v>-21.18027276915087</v>
       </c>
       <c r="F41">
-        <v>-1.882762454006989</v>
+        <v>-2.921304890979591</v>
       </c>
       <c r="G41">
-        <v>-7.514895319252603</v>
+        <v>-9.315016122644247</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-8.622062397391874</v>
       </c>
       <c r="E42">
-        <v>-17.89245572841395</v>
+        <v>-21.66875926035828</v>
       </c>
       <c r="F42">
-        <v>-1.777006444426382</v>
+        <v>-3.368354897452817</v>
       </c>
       <c r="G42">
-        <v>-7.002424292433849</v>
+        <v>-8.483593954139669</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-8.734398041375533</v>
       </c>
       <c r="E43">
-        <v>-17.3149077388977</v>
+        <v>-20.8902874075957</v>
       </c>
       <c r="F43">
-        <v>-1.660373970847017</v>
+        <v>-3.191935006576398</v>
       </c>
       <c r="G43">
-        <v>-6.695443046996879</v>
+        <v>-8.732641951723082</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-8.805958502023223</v>
       </c>
       <c r="E44">
-        <v>-17.64597994512447</v>
+        <v>-21.20333628727194</v>
       </c>
       <c r="F44">
-        <v>-1.766525940046163</v>
+        <v>-3.376144036141341</v>
       </c>
       <c r="G44">
-        <v>-6.818682447548063</v>
+        <v>-9.369349870447092</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-8.831252163426253</v>
       </c>
       <c r="E45">
-        <v>-16.61687064145936</v>
+        <v>-20.64597623488188</v>
       </c>
       <c r="F45">
-        <v>-1.877649770396911</v>
+        <v>-3.186606947441592</v>
       </c>
       <c r="G45">
-        <v>-6.398157811268069</v>
+        <v>-9.698961700979551</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-8.822633887618645</v>
       </c>
       <c r="E46">
-        <v>-16.39795515098056</v>
+        <v>-20.32693618409349</v>
       </c>
       <c r="F46">
-        <v>-1.900020660476914</v>
+        <v>-3.121107108534832</v>
       </c>
       <c r="G46">
-        <v>-6.064480547223458</v>
+        <v>-8.741077972352414</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-8.783392750631945</v>
       </c>
       <c r="E47">
-        <v>-15.50579595825541</v>
+        <v>-19.7190791180439</v>
       </c>
       <c r="F47">
-        <v>-1.830900027652518</v>
+        <v>-3.643207201701693</v>
       </c>
       <c r="G47">
-        <v>-6.475355110897126</v>
+        <v>-9.111993819875165</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-8.728656761850045</v>
       </c>
       <c r="E48">
-        <v>-15.52678996375497</v>
+        <v>-20.31509875303744</v>
       </c>
       <c r="F48">
-        <v>-2.134345089543825</v>
+        <v>-3.520868105084443</v>
       </c>
       <c r="G48">
-        <v>-6.261993678994233</v>
+        <v>-7.67428065650263</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-8.672046365087621</v>
       </c>
       <c r="E49">
-        <v>-14.660117022745</v>
+        <v>-20.09408205061908</v>
       </c>
       <c r="F49">
-        <v>-2.206564644822094</v>
+        <v>-3.650985571613981</v>
       </c>
       <c r="G49">
-        <v>-6.417484206253198</v>
+        <v>-8.496623684952224</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-8.619484381535479</v>
       </c>
       <c r="E50">
-        <v>-14.89903025444167</v>
+        <v>-19.31528414772795</v>
       </c>
       <c r="F50">
-        <v>-2.31896913117757</v>
+        <v>-3.419427061305018</v>
       </c>
       <c r="G50">
-        <v>-5.501012774927815</v>
+        <v>-8.290077350228298</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-8.587059902233937</v>
       </c>
       <c r="E51">
-        <v>-14.81860908453945</v>
+        <v>-18.41564844441614</v>
       </c>
       <c r="F51">
-        <v>-2.149705506293936</v>
+        <v>-3.528234776397539</v>
       </c>
       <c r="G51">
-        <v>-5.885923032401595</v>
+        <v>-8.684037216763027</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-8.572712655332156</v>
       </c>
       <c r="E52">
-        <v>-14.49816067833467</v>
+        <v>-17.89591548255581</v>
       </c>
       <c r="F52">
-        <v>-2.415565882385423</v>
+        <v>-3.606692766586291</v>
       </c>
       <c r="G52">
-        <v>-5.801349546706908</v>
+        <v>-8.061891359319834</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-8.583270242782566</v>
       </c>
       <c r="E53">
-        <v>-13.58793740279293</v>
+        <v>-18.71191479941995</v>
       </c>
       <c r="F53">
-        <v>-2.65658269169955</v>
+        <v>-3.476224900645369</v>
       </c>
       <c r="G53">
-        <v>-5.748781096103044</v>
+        <v>-8.873586823809029</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-8.617903545950448</v>
       </c>
       <c r="E54">
-        <v>-13.90132138954574</v>
+        <v>-17.48070422926653</v>
       </c>
       <c r="F54">
-        <v>-2.430522055842968</v>
+        <v>-3.987418708586972</v>
       </c>
       <c r="G54">
-        <v>-5.742832241415771</v>
+        <v>-8.589456005312034</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-8.669175163986919</v>
       </c>
       <c r="E55">
-        <v>-13.79035566246179</v>
+        <v>-17.06423406020311</v>
       </c>
       <c r="F55">
-        <v>-2.355838935908773</v>
+        <v>-3.727542458613308</v>
       </c>
       <c r="G55">
-        <v>-5.997074412727785</v>
+        <v>-8.318738820550047</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-8.739844777071522</v>
       </c>
       <c r="E56">
-        <v>-13.3667622037843</v>
+        <v>-16.25326587796148</v>
       </c>
       <c r="F56">
-        <v>-2.520201939237445</v>
+        <v>-3.502478348742293</v>
       </c>
       <c r="G56">
-        <v>-5.531282043813691</v>
+        <v>-9.319383428539867</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-8.816240911328217</v>
       </c>
       <c r="E57">
-        <v>-12.44352409394452</v>
+        <v>-17.37736445241149</v>
       </c>
       <c r="F57">
-        <v>-2.469787499103067</v>
+        <v>-4.079582865822444</v>
       </c>
       <c r="G57">
-        <v>-5.813693502213539</v>
+        <v>-8.669353750284513</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-8.900342132008927</v>
       </c>
       <c r="E58">
-        <v>-12.47735632325582</v>
+        <v>-16.95531067489661</v>
       </c>
       <c r="F58">
-        <v>-2.673653687136442</v>
+        <v>-4.024004383299014</v>
       </c>
       <c r="G58">
-        <v>-6.26910080489199</v>
+        <v>-9.028483449965737</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-8.987687067389702</v>
       </c>
       <c r="E59">
-        <v>-11.53590469095719</v>
+        <v>-16.15267035635509</v>
       </c>
       <c r="F59">
-        <v>-2.747495185789393</v>
+        <v>-4.068720484069535</v>
       </c>
       <c r="G59">
-        <v>-6.571422715714547</v>
+        <v>-9.543576172810488</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-9.074160377974342</v>
       </c>
       <c r="E60">
-        <v>-12.10266132691316</v>
+        <v>-16.47883369675755</v>
       </c>
       <c r="F60">
-        <v>-2.675707209927983</v>
+        <v>-3.902081955485372</v>
       </c>
       <c r="G60">
-        <v>-6.810567986631557</v>
+        <v>-9.113693492642957</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-9.165621754865848</v>
       </c>
       <c r="E61">
-        <v>-11.49541560485461</v>
+        <v>-15.12710684783799</v>
       </c>
       <c r="F61">
-        <v>-2.407909282481347</v>
+        <v>-3.780057638481185</v>
       </c>
       <c r="G61">
-        <v>-7.129735688940304</v>
+        <v>-10.36013768887234</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-9.253102640560979</v>
       </c>
       <c r="E62">
-        <v>-11.43503746091034</v>
+        <v>-15.73413520314417</v>
       </c>
       <c r="F62">
-        <v>-2.416347032846263</v>
+        <v>-3.749330178041741</v>
       </c>
       <c r="G62">
-        <v>-6.927756814627124</v>
+        <v>-9.514471737578212</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-9.3450830101555</v>
       </c>
       <c r="E63">
-        <v>-10.5670286200681</v>
+        <v>-15.13842350438316</v>
       </c>
       <c r="F63">
-        <v>-2.833244465857587</v>
+        <v>-3.651071721823872</v>
       </c>
       <c r="G63">
-        <v>-7.399586631210597</v>
+        <v>-9.313247544223707</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-9.439174896508554</v>
       </c>
       <c r="E64">
-        <v>-10.78247529945702</v>
+        <v>-15.56391892214386</v>
       </c>
       <c r="F64">
-        <v>-2.838095385368381</v>
+        <v>-3.476403828004373</v>
       </c>
       <c r="G64">
-        <v>-7.333719389626303</v>
+        <v>-10.36835058643563</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-9.534382755389599</v>
       </c>
       <c r="E65">
-        <v>-10.95494223203915</v>
+        <v>-14.91194999078555</v>
       </c>
       <c r="F65">
-        <v>-2.513840905951348</v>
+        <v>-3.572245936508276</v>
       </c>
       <c r="G65">
-        <v>-7.071891034068853</v>
+        <v>-10.38124250594269</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-9.634758486892377</v>
       </c>
       <c r="E66">
-        <v>-10.3594524285045</v>
+        <v>-14.37647605327456</v>
       </c>
       <c r="F66">
-        <v>-2.858319975507731</v>
+        <v>-3.888152129239896</v>
       </c>
       <c r="G66">
-        <v>-7.516214370319499</v>
+        <v>-9.893620169993609</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-9.729264263740257</v>
       </c>
       <c r="E67">
-        <v>-11.23083045400845</v>
+        <v>-15.77159926860963</v>
       </c>
       <c r="F67">
-        <v>-2.734229710200962</v>
+        <v>-3.673318356793455</v>
       </c>
       <c r="G67">
-        <v>-7.919558530514242</v>
+        <v>-10.74658027681438</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-9.822483310029538</v>
       </c>
       <c r="E68">
-        <v>-10.28332878043556</v>
+        <v>-14.80981025954255</v>
       </c>
       <c r="F68">
-        <v>-3.104158711473554</v>
+        <v>-3.933027276551753</v>
       </c>
       <c r="G68">
-        <v>-7.458665025388399</v>
+        <v>-10.88783358372692</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-9.906828592784478</v>
       </c>
       <c r="E69">
-        <v>-10.92026317808841</v>
+        <v>-14.5854379578845</v>
       </c>
       <c r="F69">
-        <v>-2.674173901865401</v>
+        <v>-3.767000083110857</v>
       </c>
       <c r="G69">
-        <v>-7.605132193358892</v>
+        <v>-10.94892336672066</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-9.980495738560803</v>
       </c>
       <c r="E70">
-        <v>-11.15914471046703</v>
+        <v>-14.34907425705415</v>
       </c>
       <c r="F70">
-        <v>-2.762639398647374</v>
+        <v>-3.783527669531512</v>
       </c>
       <c r="G70">
-        <v>-7.079273782577603</v>
+        <v>-10.48210725668002</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-10.04682819694676</v>
       </c>
       <c r="E71">
-        <v>-11.11846089998212</v>
+        <v>-14.6973727784061</v>
       </c>
       <c r="F71">
-        <v>-2.563276215815617</v>
+        <v>-4.257329801278148</v>
       </c>
       <c r="G71">
-        <v>-7.763670975446582</v>
+        <v>-10.26712818254832</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-10.09819050255376</v>
       </c>
       <c r="E72">
-        <v>-11.18642423788923</v>
+        <v>-14.40484694293262</v>
       </c>
       <c r="F72">
-        <v>-3.112941891045437</v>
+        <v>-3.811593585505762</v>
       </c>
       <c r="G72">
-        <v>-7.753824029546688</v>
+        <v>-10.48731455529486</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-10.14362927745147</v>
       </c>
       <c r="E73">
-        <v>-10.90429125026336</v>
+        <v>-15.83022036463892</v>
       </c>
       <c r="F73">
-        <v>-3.420352347693945</v>
+        <v>-3.923243429157288</v>
       </c>
       <c r="G73">
-        <v>-7.280770317321544</v>
+        <v>-10.60710211076551</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-10.17825292587882</v>
       </c>
       <c r="E74">
-        <v>-11.65649795378145</v>
+        <v>-15.19603475070874</v>
       </c>
       <c r="F74">
-        <v>-3.158002592655522</v>
+        <v>-4.287589234135011</v>
       </c>
       <c r="G74">
-        <v>-7.214066364239592</v>
+        <v>-10.22817023897303</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-10.20387344215513</v>
       </c>
       <c r="E75">
-        <v>-11.72228762416488</v>
+        <v>-14.99136131098406</v>
       </c>
       <c r="F75">
-        <v>-3.181894365287065</v>
+        <v>-4.399094113491048</v>
       </c>
       <c r="G75">
-        <v>-6.67534884616684</v>
+        <v>-10.47976774570813</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-10.22336452314796</v>
       </c>
       <c r="E76">
-        <v>-11.55714323405316</v>
+        <v>-14.51302765850185</v>
       </c>
       <c r="F76">
-        <v>-3.559427779317357</v>
+        <v>-4.282468266850905</v>
       </c>
       <c r="G76">
-        <v>-6.917781901086413</v>
+        <v>-10.53326478201332</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-10.2284262391334</v>
       </c>
       <c r="E77">
-        <v>-12.76124635879668</v>
+        <v>-15.57733679062859</v>
       </c>
       <c r="F77">
-        <v>-3.327867612273589</v>
+        <v>-4.4900389139096</v>
       </c>
       <c r="G77">
-        <v>-6.512718380794523</v>
+        <v>-10.83081579668845</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-10.22756914155038</v>
       </c>
       <c r="E78">
-        <v>-12.00522215169012</v>
+        <v>-16.45939748631663</v>
       </c>
       <c r="F78">
-        <v>-3.323623057701644</v>
+        <v>-4.14218756065642</v>
       </c>
       <c r="G78">
-        <v>-6.819548690039757</v>
+        <v>-9.007555818859599</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-10.21434061320074</v>
       </c>
       <c r="E79">
-        <v>-12.78755679278124</v>
+        <v>-15.940669845686</v>
       </c>
       <c r="F79">
-        <v>-3.671259035430095</v>
+        <v>-4.544765006375549</v>
       </c>
       <c r="G79">
-        <v>-6.671634503361549</v>
+        <v>-8.790197859097303</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-10.19114728714614</v>
       </c>
       <c r="E80">
-        <v>-13.27238427699045</v>
+        <v>-16.30113637669657</v>
       </c>
       <c r="F80">
-        <v>-3.580373049097142</v>
+        <v>-4.425871918153944</v>
       </c>
       <c r="G80">
-        <v>-5.89310234517366</v>
+        <v>-9.021471479493204</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-10.1591727604418</v>
       </c>
       <c r="E81">
-        <v>-13.39883738518063</v>
+        <v>-17.65295832357029</v>
       </c>
       <c r="F81">
-        <v>-3.690234447526024</v>
+        <v>-4.798379627151451</v>
       </c>
       <c r="G81">
-        <v>-5.703946484714791</v>
+        <v>-9.369927365441555</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-10.10920866336014</v>
       </c>
       <c r="E82">
-        <v>-13.90031606831604</v>
+        <v>-17.88240704459093</v>
       </c>
       <c r="F82">
-        <v>-3.784082675691388</v>
+        <v>-4.574409790619534</v>
       </c>
       <c r="G82">
-        <v>-5.810605872726102</v>
+        <v>-8.590181155276671</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-10.0480246469706</v>
       </c>
       <c r="E83">
-        <v>-15.10182437745316</v>
+        <v>-18.67535190028202</v>
       </c>
       <c r="F83">
-        <v>-4.082220387632958</v>
+        <v>-4.768229538791758</v>
       </c>
       <c r="G83">
-        <v>-6.156144752708106</v>
+        <v>-9.643942177870782</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-9.966388595794292</v>
       </c>
       <c r="E84">
-        <v>-15.94653421952594</v>
+        <v>-18.98885362735904</v>
       </c>
       <c r="F84">
-        <v>-4.317953041284627</v>
+        <v>-4.958266133035395</v>
       </c>
       <c r="G84">
-        <v>-5.984704207448678</v>
+        <v>-9.410040299005766</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-9.868085728252584</v>
       </c>
       <c r="E85">
-        <v>-17.07495748665327</v>
+        <v>-19.40537813811055</v>
       </c>
       <c r="F85">
-        <v>-4.458314099117184</v>
+        <v>-5.226475759081222</v>
       </c>
       <c r="G85">
-        <v>-5.83643564884205</v>
+        <v>-8.652133899540546</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-9.75614074473793</v>
       </c>
       <c r="E86">
-        <v>-17.61462931956937</v>
+        <v>-20.53522787455029</v>
       </c>
       <c r="F86">
-        <v>-4.331990555292468</v>
+        <v>-5.661555856583995</v>
       </c>
       <c r="G86">
-        <v>-6.076427474921396</v>
+        <v>-8.471450153148163</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-9.630142195461637</v>
       </c>
       <c r="E87">
-        <v>-18.20104858966665</v>
+        <v>-22.72421522580002</v>
       </c>
       <c r="F87">
-        <v>-4.625766084490896</v>
+        <v>-5.501772068257998</v>
       </c>
       <c r="G87">
-        <v>-5.710348147977268</v>
+        <v>-9.22464143723246</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-9.507472837650068</v>
       </c>
       <c r="E88">
-        <v>-19.33530000284185</v>
+        <v>-22.78475186633455</v>
       </c>
       <c r="F88">
-        <v>-4.702961642757781</v>
+        <v>-5.594086159993378</v>
       </c>
       <c r="G88">
-        <v>-6.063627429618002</v>
+        <v>-8.709591370267983</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-9.391160999141569</v>
       </c>
       <c r="E89">
-        <v>-21.5179293765848</v>
+        <v>-23.22281832794055</v>
       </c>
       <c r="F89">
-        <v>-4.836215308274318</v>
+        <v>-5.898888916057873</v>
       </c>
       <c r="G89">
-        <v>-5.686828351839169</v>
+        <v>-8.190869616378487</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-9.299770364696137</v>
       </c>
       <c r="E90">
-        <v>-22.85522397884192</v>
+        <v>-25.15692051966855</v>
       </c>
       <c r="F90">
-        <v>-4.552096886257727</v>
+        <v>-5.830948706782466</v>
       </c>
       <c r="G90">
-        <v>-6.131903087826928</v>
+        <v>-9.195179348850207</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-9.243271940823705</v>
       </c>
       <c r="E91">
-        <v>-23.96960444807146</v>
+        <v>-26.81703192003645</v>
       </c>
       <c r="F91">
-        <v>-4.777268683891106</v>
+        <v>-5.812847222296491</v>
       </c>
       <c r="G91">
-        <v>-5.76617485158966</v>
+        <v>-9.086577477675705</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-9.225923317867691</v>
       </c>
       <c r="E92">
-        <v>-25.92661166133026</v>
+        <v>-29.20990022805951</v>
       </c>
       <c r="F92">
-        <v>-4.998523132076645</v>
+        <v>-5.54699181640942</v>
       </c>
       <c r="G92">
-        <v>-6.121458959603215</v>
+        <v>-8.931208355614439</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-9.260433761957252</v>
       </c>
       <c r="E93">
-        <v>-27.85644803054302</v>
+        <v>-30.63677031042535</v>
       </c>
       <c r="F93">
-        <v>-4.931985348814178</v>
+        <v>-5.858759485596654</v>
       </c>
       <c r="G93">
-        <v>-6.385141205341752</v>
+        <v>-8.69791350273792</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-9.337635851204022</v>
       </c>
       <c r="E94">
-        <v>-29.87707577513558</v>
+        <v>-31.647897043806</v>
       </c>
       <c r="F94">
-        <v>-4.968187489418725</v>
+        <v>-5.86367915960188</v>
       </c>
       <c r="G94">
-        <v>-6.372118036972316</v>
+        <v>-9.629944486698191</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-9.461951266724949</v>
       </c>
       <c r="E95">
-        <v>-31.60970389402531</v>
+        <v>-35.36959850040284</v>
       </c>
       <c r="F95">
-        <v>-4.958084720574182</v>
+        <v>-5.901359107653021</v>
       </c>
       <c r="G95">
-        <v>-6.736107225783078</v>
+        <v>-10.36074143363928</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-9.62375836733694</v>
       </c>
       <c r="E96">
-        <v>-34.87126257822876</v>
+        <v>-36.57189023554329</v>
       </c>
       <c r="F96">
-        <v>-5.049526541434414</v>
+        <v>-5.798586877457297</v>
       </c>
       <c r="G96">
-        <v>-7.335327188190432</v>
+        <v>-10.26410289627051</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-9.809959813937809</v>
       </c>
       <c r="E97">
-        <v>-36.53264647979282</v>
+        <v>-38.5362856541456</v>
       </c>
       <c r="F97">
-        <v>-4.900194264629539</v>
+        <v>-5.995680333605383</v>
       </c>
       <c r="G97">
-        <v>-7.239239896043652</v>
+        <v>-10.57288225112206</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-10.01739865657869</v>
       </c>
       <c r="E98">
-        <v>-38.38289265408378</v>
+        <v>-41.38818725843016</v>
       </c>
       <c r="F98">
-        <v>-4.885972024690874</v>
+        <v>-5.587905710801091</v>
       </c>
       <c r="G98">
-        <v>-7.812456177592407</v>
+        <v>-11.72752114933974</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-10.22105664199982</v>
       </c>
       <c r="E99">
-        <v>-40.68439220629107</v>
+        <v>-42.89500528516442</v>
       </c>
       <c r="F99">
-        <v>-4.735096499414583</v>
+        <v>-5.825448347227877</v>
       </c>
       <c r="G99">
-        <v>-7.975168673503711</v>
+        <v>-10.64968252294242</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-10.42199406038003</v>
       </c>
       <c r="E100">
-        <v>-43.41471786889172</v>
+        <v>-45.63653212822304</v>
       </c>
       <c r="F100">
-        <v>-4.708618563751499</v>
+        <v>-5.455392605742657</v>
       </c>
       <c r="G100">
-        <v>-8.419879193898371</v>
+        <v>-11.08217377424971</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-10.59455031062035</v>
       </c>
       <c r="E101">
-        <v>-45.9418599597162</v>
+        <v>-48.08895213368397</v>
       </c>
       <c r="F101">
-        <v>-4.521725623801486</v>
+        <v>-5.031266838774505</v>
       </c>
       <c r="G101">
-        <v>-9.406358768416069</v>
+        <v>-12.52909404531805</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-10.74066120341519</v>
       </c>
       <c r="E102">
-        <v>-48.76949573603067</v>
+        <v>-50.62473568503359</v>
       </c>
       <c r="F102">
-        <v>-4.317795651478096</v>
+        <v>-5.07995247613924</v>
       </c>
       <c r="G102">
-        <v>-9.196616523893244</v>
+        <v>-12.63127128467915</v>
       </c>
     </row>
   </sheetData>
